--- a/debug_bbox/layout_ranking_report.xlsx
+++ b/debug_bbox/layout_ranking_report.xlsx
@@ -1180,6 +1180,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1472,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1500,7 +1525,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Runs Analyzed: 35  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
+          <t xml:space="preserve">  Total Runs Analyzed: 36  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2272,11 @@
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_5_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt22_agent_size35.txt</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>88.77088473050095</v>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv1_attempt25.txt</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>90</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>1</v>
@@ -2266,17 +2291,17 @@
         <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>58.5</v>
+        <v>69.5</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+        <v>0.066</v>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
         </is>
       </c>
     </row>
@@ -2289,26 +2314,26 @@
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_input_SecondBedroom-6482.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_5_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt22_agent_size35.txt</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>86.53160281605736</v>
+        <v>88.77088473050095</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.1091</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>40.4</v>
+        <v>58.5</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>1</v>
@@ -2331,36 +2356,36 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt6_weight10_clip10.1.txt</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>70</v>
+          <t>debug_bbox_input_SecondBedroom-6482.txt</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>86.53160281605736</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0</v>
+        <v>0.1091</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>68.5</v>
+        <v>40.4</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>MINOR ISSUES</t>
+        <v>0</v>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2398,7 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt5_weight10_clip10.1.txt</t>
+          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt6_weight10_clip10.1.txt</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
@@ -2392,13 +2417,13 @@
         <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>66.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="L25" s="15" t="inlineStr">
         <is>
@@ -2415,11 +2440,11 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.2_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt16.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt5_weight10_clip10.1.txt</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>69.83852912755376</v>
+        <v>70</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>2</v>
@@ -2434,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>1</v>
@@ -2457,11 +2482,11 @@
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.4_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt15.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.2_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt16.txt</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>69.80709213936994</v>
+        <v>69.83852912755376</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>2</v>
@@ -2476,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>65.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J27" s="9" t="n">
         <v>1</v>
@@ -2499,11 +2524,11 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt21.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.4_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt15.txt</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>69.75767609020983</v>
+        <v>69.80709213936994</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>2</v>
@@ -2518,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>1</v>
@@ -2541,17 +2566,17 @@
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt21.txt</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>65.40858016448331</v>
+        <v>69.75767609020983</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.1312</v>
+        <v>0</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
@@ -2560,13 +2585,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>70</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.247</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15" t="inlineStr">
         <is>
@@ -2583,32 +2608,32 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss.txt</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>51.87146416439781</v>
+        <v>65.40858016448331</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.1312</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1121</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
@@ -2625,26 +2650,26 @@
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>42.53917712747405</v>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss.txt</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>51.87146416439781</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0024</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.6827</v>
+        <v>0.1121</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>64.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>1</v>
@@ -2652,9 +2677,9 @@
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="17" t="inlineStr">
-        <is>
-          <t>SEVERE COLLISIONS</t>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <t>MINOR ISSUES</t>
         </is>
       </c>
     </row>
@@ -2667,26 +2692,26 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_attempt2.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>31.61607091349578</v>
+        <v>42.53917712747405</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.0089</v>
+        <v>0.0002</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1136</v>
+        <v>0.6827</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>1</v>
@@ -2709,26 +2734,26 @@
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_attempt2.txt</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
-        <v>21.58015658181118</v>
+        <v>31.61607091349578</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.0571</v>
+        <v>0.0089</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.6384</v>
+        <v>0.1136</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>63.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>1</v>
@@ -2751,26 +2776,26 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>7.713943629027742</v>
+        <v>21.58015658181118</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2967</v>
+        <v>0.6384</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>61.6</v>
+        <v>63.6</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>1</v>
@@ -2793,7 +2818,7 @@
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_1_fixed.txt</t>
+          <t>debug_bbox__physc_colloss_scale_1.txt</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
@@ -2835,7 +2860,7 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_10.txt</t>
+          <t>debug_bbox__physc_colloss_scale_1_fixed.txt</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
@@ -2877,7 +2902,7 @@
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_total_guidance_loss_0.txt</t>
+          <t>debug_bbox__physc_colloss_scale_10.txt</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
@@ -2919,23 +2944,23 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_fixed_1_strength_10.0_clip_10.1.txt</t>
+          <t>debug_bbox_total_guidance_loss_0.txt</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>0</v>
+        <v>7.713943629027742</v>
       </c>
       <c r="E38" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.5446</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.4422</v>
+        <v>0.2967</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>61.6</v>
@@ -2961,7 +2986,7 @@
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene.txt</t>
+          <t>debug_bbox_fixed_1_strength_10.0_clip_10.1.txt</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
@@ -2971,16 +2996,16 @@
         <v>2</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.1282</v>
+        <v>0.5446</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>2.0056</v>
+        <v>0.4422</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>93.5</v>
+        <v>61.6</v>
       </c>
       <c r="J39" s="9" t="n">
         <v>1</v>
@@ -3003,34 +3028,76 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene.txt</t>
         </is>
       </c>
       <c r="D40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.1282</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H40" s="4" t="n">
+        <v>2.0056</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="17" t="inlineStr">
+        <is>
+          <t>SEVERE COLLISIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="115" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>#36</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1.txt</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" s="9" t="n">
         <v>2.1998</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I41" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="J40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="17" t="inlineStr">
+      <c r="J41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="17" t="inlineStr">
         <is>
           <t>SEVERE COLLISIONS</t>
         </is>

--- a/debug_bbox/layout_ranking_report.xlsx
+++ b/debug_bbox/layout_ranking_report.xlsx
@@ -1205,6 +1205,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1497,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1525,7 +1550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Runs Analyzed: 36  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
+          <t xml:space="preserve">  Total Runs Analyzed: 37  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
         </is>
       </c>
     </row>
@@ -1852,32 +1877,32 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_aabb_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt8_weight1_clip10.1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv2_attempt26.txt</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>90</v>
+        <v>94.97411878009191</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1894,7 +1919,7 @@
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt7_weight1_clip10.1.txt</t>
+          <t>debug_bbox_physc_colloss_aabb_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt8_weight1_clip10.1.txt</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
@@ -1913,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>68.3</v>
+        <v>72</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -1936,7 +1961,7 @@
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt18.txt</t>
+          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt7_weight1_clip10.1.txt</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -1955,13 +1980,13 @@
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>71.5</v>
+        <v>68.3</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -1978,7 +2003,7 @@
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt19.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt18.txt</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -1997,13 +2022,13 @@
         <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>72.5</v>
+        <v>71.5</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.187</v>
+        <v>0.174</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2020,7 +2045,7 @@
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt2.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt19.txt</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -2039,13 +2064,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.008</v>
+        <v>0.187</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2062,7 +2087,7 @@
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt3_weight10.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt2.txt</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
@@ -2087,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2104,7 +2129,7 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt4_weight10_clip20.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt3_weight10.txt</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -2123,13 +2148,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2146,7 +2171,7 @@
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt9.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt4_weight10_clip20.txt</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -2165,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>68.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2188,7 +2213,7 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt10.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt9.txt</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
@@ -2207,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>1</v>
@@ -2230,7 +2255,7 @@
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt23.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt10.txt</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -2249,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>69.2</v>
+        <v>68.2</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2272,7 +2297,7 @@
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv1_attempt25.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt23.txt</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
@@ -2291,13 +2316,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.066</v>
+        <v>0.05</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2314,11 +2339,11 @@
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_5_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt22_agent_size35.txt</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>88.77088473050095</v>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv1_attempt25.txt</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>90</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>1</v>
@@ -2333,17 +2358,17 @@
         <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>58.5</v>
+        <v>69.5</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+        <v>0.066</v>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
         </is>
       </c>
     </row>
@@ -2356,26 +2381,26 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_input_SecondBedroom-6482.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_5_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt22_agent_size35.txt</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>86.53160281605736</v>
+        <v>88.77088473050095</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.1091</v>
+        <v>0</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>40.4</v>
+        <v>58.5</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>1</v>
@@ -2398,36 +2423,36 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt6_weight10_clip10.1.txt</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>70</v>
+          <t>debug_bbox_input_SecondBedroom-6482.txt</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>86.53160281605736</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0</v>
+        <v>0.1091</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>68.5</v>
+        <v>40.4</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>MINOR ISSUES</t>
+        <v>0</v>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2465,7 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt5_weight10_clip10.1.txt</t>
+          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt6_weight10_clip10.1.txt</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
@@ -2459,13 +2484,13 @@
         <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
@@ -2482,11 +2507,11 @@
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.2_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt16.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt5_weight10_clip10.1.txt</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>69.83852912755376</v>
+        <v>70</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>2</v>
@@ -2501,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>65.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J27" s="9" t="n">
         <v>1</v>
@@ -2524,11 +2549,11 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.4_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt15.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.2_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt16.txt</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>69.80709213936994</v>
+        <v>69.83852912755376</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>2</v>
@@ -2543,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>1</v>
@@ -2566,11 +2591,11 @@
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt21.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.4_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt15.txt</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>69.75767609020983</v>
+        <v>69.80709213936994</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>2</v>
@@ -2585,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>65.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>1</v>
@@ -2608,17 +2633,17 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt21.txt</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>65.40858016448331</v>
+        <v>69.75767609020983</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1312</v>
+        <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>0</v>
@@ -2627,13 +2652,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>70</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.247</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
@@ -2650,32 +2675,32 @@
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss.txt</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>51.87146416439781</v>
+        <v>65.40858016448331</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.0024</v>
+        <v>0.1312</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.1121</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>65.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="L31" s="15" t="inlineStr">
         <is>
@@ -2692,26 +2717,26 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>42.53917712747405</v>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss.txt</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>51.87146416439781</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.0002</v>
+        <v>0.0024</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.6827</v>
+        <v>0.1121</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>1</v>
@@ -2719,9 +2744,9 @@
       <c r="K32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="17" t="inlineStr">
-        <is>
-          <t>SEVERE COLLISIONS</t>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
+          <t>MINOR ISSUES</t>
         </is>
       </c>
     </row>
@@ -2734,26 +2759,26 @@
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_attempt2.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
-        <v>31.61607091349578</v>
+        <v>42.53917712747405</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.0089</v>
+        <v>0.0002</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.1136</v>
+        <v>0.6827</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>65.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>1</v>
@@ -2776,26 +2801,26 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_attempt2.txt</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>21.58015658181118</v>
+        <v>31.61607091349578</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.0571</v>
+        <v>0.0089</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.6384</v>
+        <v>0.1136</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>63.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>1</v>
@@ -2818,26 +2843,26 @@
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>7.713943629027742</v>
+        <v>21.58015658181118</v>
       </c>
       <c r="E35" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.2967</v>
+        <v>0.6384</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>61.6</v>
+        <v>63.6</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>1</v>
@@ -2860,7 +2885,7 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_1_fixed.txt</t>
+          <t>debug_bbox__physc_colloss_scale_1.txt</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
@@ -2902,7 +2927,7 @@
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_10.txt</t>
+          <t>debug_bbox__physc_colloss_scale_1_fixed.txt</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
@@ -2944,7 +2969,7 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_total_guidance_loss_0.txt</t>
+          <t>debug_bbox__physc_colloss_scale_10.txt</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
@@ -2986,23 +3011,23 @@
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_fixed_1_strength_10.0_clip_10.1.txt</t>
+          <t>debug_bbox_total_guidance_loss_0.txt</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
-        <v>0</v>
+        <v>7.713943629027742</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.5446</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.4422</v>
+        <v>0.2967</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>61.6</v>
@@ -3028,7 +3053,7 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene.txt</t>
+          <t>debug_bbox_fixed_1_strength_10.0_clip_10.1.txt</t>
         </is>
       </c>
       <c r="D40" s="16" t="n">
@@ -3038,16 +3063,16 @@
         <v>2</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.1282</v>
+        <v>0.5446</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2.0056</v>
+        <v>0.4422</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>93.5</v>
+        <v>61.6</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>1</v>
@@ -3070,34 +3095,76 @@
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene.txt</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>0.0071</v>
+        <v>0.1282</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H41" s="9" t="n">
+        <v>2.0056</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="17" t="inlineStr">
+        <is>
+          <t>SEVERE COLLISIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="115" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>#37</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1.txt</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>2.1998</v>
       </c>
-      <c r="I41" s="9" t="n">
+      <c r="I42" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="J41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="17" t="inlineStr">
+      <c r="J42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="17" t="inlineStr">
         <is>
           <t>SEVERE COLLISIONS</t>
         </is>

--- a/debug_bbox/layout_ranking_report.xlsx
+++ b/debug_bbox/layout_ranking_report.xlsx
@@ -1230,6 +1230,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1522,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1550,7 +1575,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Runs Analyzed: 37  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
+          <t xml:space="preserve">  Total Runs Analyzed: 38  |  Metrics: Furniture Overlaps, OBB Overlap Area, Out-of-Bounds Protrusions, Free Floor %, Walkability</t>
         </is>
       </c>
     </row>
@@ -1877,11 +1902,11 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv2_attempt26.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_5_ignore_scene_floor_room_outer_loss_walkable_loss_mixv2_attempt27.txt</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>94.97411878009191</v>
+        <v>100</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -1890,13 +1915,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>71.3</v>
+        <v>58.8</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>1</v>
@@ -1919,32 +1944,32 @@
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_aabb_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt8_weight1_clip10.1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv2_attempt26.txt</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>90</v>
+        <v>94.97411878009191</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -1961,7 +1986,7 @@
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt7_weight1_clip10.1.txt</t>
+          <t>debug_bbox_physc_colloss_aabb_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt8_weight1_clip10.1.txt</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -1980,13 +2005,13 @@
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>68.3</v>
+        <v>72</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2003,7 +2028,7 @@
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt18.txt</t>
+          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt7_weight1_clip10.1.txt</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -2022,13 +2047,13 @@
         <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>71.5</v>
+        <v>68.3</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2045,7 +2070,7 @@
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt19.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt18.txt</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -2064,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>72.5</v>
+        <v>71.5</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.187</v>
+        <v>0.174</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2087,7 +2112,7 @@
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt2.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.8_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt19.txt</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
@@ -2106,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>68.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.008</v>
+        <v>0.187</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2129,7 +2154,7 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt3_weight10.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt2.txt</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -2154,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2171,7 +2196,7 @@
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt4_weight10_clip20.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt3_weight10.txt</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -2190,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>71.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2213,7 +2238,7 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt9.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt4_weight10_clip20.txt</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
@@ -2232,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>68.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2255,7 +2280,7 @@
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt10.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt9.txt</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -2274,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>1</v>
@@ -2297,7 +2322,7 @@
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt23.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt10.txt</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
@@ -2316,13 +2341,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>69.2</v>
+        <v>68.2</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -2339,7 +2364,7 @@
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv1_attempt25.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt23.txt</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
@@ -2358,13 +2383,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.066</v>
+        <v>0.05</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -2381,11 +2406,11 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_5_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt22_agent_size35.txt</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>88.77088473050095</v>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_mixv1_attempt25.txt</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>90</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>1</v>
@@ -2400,17 +2425,17 @@
         <v>0</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>58.5</v>
+        <v>69.5</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>GOOD</t>
+        <v>0.066</v>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>EXCELLENT</t>
         </is>
       </c>
     </row>
@@ -2423,26 +2448,26 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_input_SecondBedroom-6482.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_5_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt22_agent_size35.txt</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>86.53160281605736</v>
+        <v>88.77088473050095</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.1091</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>40.4</v>
+        <v>58.5</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>1</v>
@@ -2465,36 +2490,36 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt6_weight10_clip10.1.txt</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>70</v>
+          <t>debug_bbox_input_SecondBedroom-6482.txt</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>86.53160281605736</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0</v>
+        <v>0.1091</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>68.5</v>
+        <v>40.4</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>MINOR ISSUES</t>
+        <v>0</v>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>GOOD</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2532,7 @@
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt5_weight10_clip10.1.txt</t>
+          <t>debug_bbox_physc_colloss_obb_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_gaussv1_attempt6_weight10_clip10.1.txt</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
@@ -2526,13 +2551,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>66.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="J27" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="L27" s="15" t="inlineStr">
         <is>
@@ -2549,11 +2574,11 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.2_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt16.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.95_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt5_weight10_clip10.1.txt</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>69.83852912755376</v>
+        <v>70</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>2</v>
@@ -2568,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>1</v>
@@ -2591,11 +2616,11 @@
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.4_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt15.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.2_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt16.txt</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>69.80709213936994</v>
+        <v>69.83852912755376</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>2</v>
@@ -2610,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>65.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>1</v>
@@ -2633,11 +2658,11 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt21.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.4_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_attempt15.txt</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>69.75767609020983</v>
+        <v>69.80709213936994</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>2</v>
@@ -2652,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>1</v>
@@ -2675,17 +2700,17 @@
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss_v3_attempt21.txt</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>65.40858016448331</v>
+        <v>69.75767609020983</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.1312</v>
+        <v>0</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
@@ -2694,13 +2719,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>70</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.247</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15" t="inlineStr">
         <is>
@@ -2717,32 +2742,32 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_walkable_loss.txt</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>51.87146416439781</v>
+        <v>65.40858016448331</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.1312</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1121</v>
+        <v>0</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
@@ -2759,26 +2784,26 @@
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>42.53917712747405</v>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss.txt</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>51.87146416439781</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>0.0002</v>
+        <v>0.0024</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.6827</v>
+        <v>0.1121</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>64.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>1</v>
@@ -2786,9 +2811,9 @@
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>SEVERE COLLISIONS</t>
+      <c r="L33" s="15" t="inlineStr">
+        <is>
+          <t>MINOR ISSUES</t>
         </is>
       </c>
     </row>
@@ -2801,26 +2826,26 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_attempt2.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>31.61607091349578</v>
+        <v>42.53917712747405</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.0089</v>
+        <v>0.0002</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1136</v>
+        <v>0.6827</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>1</v>
@@ -2843,26 +2868,26 @@
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1_ignore_scene_floor_room_outer_loss_attempt2.txt</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>21.58015658181118</v>
+        <v>31.61607091349578</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.0571</v>
+        <v>0.0089</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.6384</v>
+        <v>0.1136</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>63.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>1</v>
@@ -2885,26 +2910,26 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene_floor.txt</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>7.713943629027742</v>
+        <v>21.58015658181118</v>
       </c>
       <c r="E36" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.2967</v>
+        <v>0.6384</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>61.6</v>
+        <v>63.6</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>1</v>
@@ -2927,7 +2952,7 @@
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_1_fixed.txt</t>
+          <t>debug_bbox__physc_colloss_scale_1.txt</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
@@ -2969,7 +2994,7 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox__physc_colloss_scale_10.txt</t>
+          <t>debug_bbox__physc_colloss_scale_1_fixed.txt</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
@@ -3011,7 +3036,7 @@
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_total_guidance_loss_0.txt</t>
+          <t>debug_bbox__physc_colloss_scale_10.txt</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
@@ -3053,23 +3078,23 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_fixed_1_strength_10.0_clip_10.1.txt</t>
+          <t>debug_bbox_total_guidance_loss_0.txt</t>
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>0</v>
+        <v>7.713943629027742</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.5446</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.4422</v>
+        <v>0.2967</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>61.6</v>
@@ -3095,7 +3120,7 @@
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene.txt</t>
+          <t>debug_bbox_fixed_1_strength_10.0_clip_10.1.txt</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
@@ -3105,16 +3130,16 @@
         <v>2</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>0.1282</v>
+        <v>0.5446</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>2.0056</v>
+        <v>0.4422</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>93.5</v>
+        <v>61.6</v>
       </c>
       <c r="J41" s="9" t="n">
         <v>1</v>
@@ -3137,34 +3162,76 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1.txt</t>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_10_clip_10.1_start_0.9_interval_1_ignore_scene.txt</t>
         </is>
       </c>
       <c r="D42" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.1282</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H42" s="4" t="n">
+        <v>2.0056</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="17" t="inlineStr">
+        <is>
+          <t>SEVERE COLLISIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="115" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>debug_bbox_physc_colloss_walk_room_scale_1_strength_20_clip_10.1_start_0.9_interval_1.txt</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="9" t="n">
         <v>2.1998</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="I43" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="J42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="17" t="inlineStr">
+      <c r="J43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="17" t="inlineStr">
         <is>
           <t>SEVERE COLLISIONS</t>
         </is>
